--- a/Test upload format/MSME/MSME_Continuity - 3.xlsx
+++ b/Test upload format/MSME/MSME_Continuity - 3.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12180"/>
+    <workbookView windowWidth="24000" windowHeight="9600"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="29">
   <si>
     <t>CGPAN</t>
   </si>
@@ -53,37 +53,67 @@
     <t>NPAInterestAmount</t>
   </si>
   <si>
-    <t>CGMSMGEN0605202600504017</t>
-  </si>
-  <si>
-    <t>loan01</t>
+    <t>CGMSMGEN2209202600357196</t>
+  </si>
+  <si>
+    <t>Aloan05</t>
   </si>
   <si>
     <t>Standard</t>
   </si>
   <si>
-    <t>CGMSMGEN0605202600504018</t>
-  </si>
-  <si>
-    <t>loan02</t>
-  </si>
-  <si>
-    <t>CGMSMGEN0605202600504019</t>
-  </si>
-  <si>
-    <t>loan03</t>
-  </si>
-  <si>
-    <t>CGMSMGEN0605202600504020</t>
-  </si>
-  <si>
-    <t>loan04</t>
-  </si>
-  <si>
-    <t>Close</t>
-  </si>
-  <si>
-    <t>28-02-2029</t>
+    <t>CGMSMGEN2209202600357197</t>
+  </si>
+  <si>
+    <t>Aloan06</t>
+  </si>
+  <si>
+    <t>CGMSMGEN2209202600357198</t>
+  </si>
+  <si>
+    <t>Aloan07</t>
+  </si>
+  <si>
+    <t>CGMSMGEN2209202600357202</t>
+  </si>
+  <si>
+    <t>Aloan11</t>
+  </si>
+  <si>
+    <t>CGMSMGEN2209202600357203</t>
+  </si>
+  <si>
+    <t>Aloan12</t>
+  </si>
+  <si>
+    <t>CGMSMGEN2209202600357208</t>
+  </si>
+  <si>
+    <t>Aloan17</t>
+  </si>
+  <si>
+    <t>CGMSMGEN2209202600357209</t>
+  </si>
+  <si>
+    <t>Aloan18</t>
+  </si>
+  <si>
+    <t>CGMSMGEN2209202600357210</t>
+  </si>
+  <si>
+    <t>Aloan19</t>
+  </si>
+  <si>
+    <t>CGMSMGEN2209202600357214</t>
+  </si>
+  <si>
+    <t>Aloan23</t>
+  </si>
+  <si>
+    <t>CGMSMGEN2209202600357215</t>
+  </si>
+  <si>
+    <t>Aloan24</t>
   </si>
 </sst>
 </file>
@@ -470,12 +500,36 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="11">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -600,7 +654,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -612,34 +666,34 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -725,7 +779,7 @@
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -742,7 +796,8 @@
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1009,8 +1064,8 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
-  <sheetFormatPr defaultColWidth="12.6666666666667" defaultRowHeight="12.75" outlineLevelRow="4" outlineLevelCol="7"/>
+  <dimension ref="A1:H11"/>
+  <sheetFormatPr defaultColWidth="12.6666666666667" defaultRowHeight="12.75" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="33.4285714285714" style="3" customWidth="1"/>
     <col min="2" max="2" width="22.7809523809524" style="3" customWidth="1"/>
@@ -1053,74 +1108,174 @@
       <c r="A2" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C2" s="6">
-        <v>1000012.79</v>
+        <v>600000000</v>
       </c>
       <c r="D2" s="6">
-        <v>1001.79</v>
+        <v>0</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="7"/>
+      <c r="F2" s="8"/>
     </row>
     <row r="3" s="2" customFormat="1" ht="15" spans="1:8">
       <c r="A3" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="7" t="s">
         <v>12</v>
       </c>
       <c r="C3" s="6">
-        <v>1000043.02</v>
+        <v>500000000</v>
       </c>
       <c r="D3" s="6">
-        <v>100043.02</v>
+        <v>0</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F3" s="8"/>
+      <c r="F3" s="9"/>
     </row>
     <row r="4" s="2" customFormat="1" ht="15" spans="1:8">
       <c r="A4" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="7" t="s">
         <v>14</v>
       </c>
       <c r="C4" s="6">
-        <v>200300.33</v>
+        <v>200000000</v>
       </c>
       <c r="D4" s="6">
-        <v>200200.33</v>
+        <v>0</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F4" s="7"/>
+      <c r="F4" s="8"/>
     </row>
     <row r="5" s="2" customFormat="1" ht="15" spans="1:8">
       <c r="A5" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="7" t="s">
         <v>16</v>
       </c>
       <c r="C5" s="6">
-        <v>20010.65</v>
+        <v>180000000</v>
       </c>
       <c r="D5" s="6">
-        <v>20300.65</v>
+        <v>0</v>
       </c>
       <c r="E5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" s="8"/>
+    </row>
+    <row r="6" ht="15" spans="1:8">
+      <c r="A6" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="B6" s="7" t="s">
         <v>18</v>
+      </c>
+      <c r="C6" s="6">
+        <v>20000000</v>
+      </c>
+      <c r="D6" s="6">
+        <v>0</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" ht="15" spans="1:8">
+      <c r="A7" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" s="6">
+        <v>600000000</v>
+      </c>
+      <c r="D7" s="6">
+        <v>0</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" ht="15" spans="1:8">
+      <c r="A8" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" s="6">
+        <v>500000000</v>
+      </c>
+      <c r="D8" s="6">
+        <v>0</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" ht="15" spans="1:8">
+      <c r="A9" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" s="6">
+        <v>200000000</v>
+      </c>
+      <c r="D9" s="6">
+        <v>0</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" ht="15" spans="1:8">
+      <c r="A10" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" s="6">
+        <v>180000000</v>
+      </c>
+      <c r="D10" s="6">
+        <v>0</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" ht="15" spans="1:8">
+      <c r="A11" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C11" s="6">
+        <v>20000000</v>
+      </c>
+      <c r="D11" s="6">
+        <v>0</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
